--- a/data/trans_dic/P1417-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1417-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,8</t>
+          <t>0,28; 1,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,22</t>
+          <t>0,92; 2,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,71</t>
+          <t>0,87; 2,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,95</t>
+          <t>1,49; 4,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,53</t>
+          <t>1,83; 4,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,94</t>
+          <t>2,93; 5,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,63</t>
+          <t>0,52; 1,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,03</t>
+          <t>0,78; 2,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,66</t>
+          <t>1,29; 2,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,37</t>
+          <t>2,13; 3,56</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,02</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,39</t>
+          <t>0,31; 1,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,51</t>
+          <t>0,39; 1,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,97</t>
+          <t>0,95; 2,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,26</t>
+          <t>0,73; 2,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,68</t>
+          <t>2,26; 4,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,15</t>
+          <t>1,28; 3,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,34</t>
+          <t>3,27; 5,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,32</t>
+          <t>0,49; 1,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,67</t>
+          <t>1,44; 2,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,06</t>
+          <t>1,0; 2,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,28</t>
+          <t>2,26; 3,51</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,41</t>
+          <t>0,22; 1,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,02</t>
+          <t>0,51; 1,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,16</t>
+          <t>1,65; 4,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,23</t>
+          <t>1,7; 4,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,52</t>
+          <t>1,24; 3,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,78</t>
+          <t>4,46; 7,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,4</t>
+          <t>0,95; 2,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,2</t>
+          <t>0,89; 2,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,14</t>
+          <t>0,9; 2,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,28</t>
+          <t>2,63; 4,49</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,2</t>
+          <t>0,19; 1,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,28</t>
+          <t>0,3; 1,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,63</t>
+          <t>0,46; 1,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,45</t>
+          <t>0,81; 2,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,41</t>
+          <t>1,6; 3,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,95</t>
+          <t>1,85; 3,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,35</t>
+          <t>3,36; 5,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,55</t>
+          <t>0,67; 1,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,15</t>
+          <t>1,1; 2,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,1</t>
+          <t>1,0; 2,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,26</t>
+          <t>2,22; 3,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,67</t>
+          <t>0,22; 0,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,68</t>
+          <t>0,24; 0,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,87</t>
+          <t>0,36; 0,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,45</t>
+          <t>0,97; 1,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,2</t>
+          <t>1,29; 2,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,34</t>
+          <t>2,22; 3,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,04</t>
+          <t>1,95; 3,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,94</t>
+          <t>3,93; 5,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,35</t>
+          <t>0,81; 1,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,89</t>
+          <t>1,35; 1,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,88</t>
+          <t>1,26; 1,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,09</t>
+          <t>2,6; 3,29</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33853</t>
+          <t>39113</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 9088</t>
+          <t>0; 8711</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5336</t>
+          <t>0; 4895</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1756; 12157</t>
+          <t>1897; 11889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4807; 14098</t>
+          <t>6309; 18292</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5560; 18678</t>
+          <t>5977; 19398</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9574; 27539</t>
+          <t>10411; 28062</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11436; 30501</t>
+          <t>12333; 31611</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18143; 33366</t>
+          <t>21441; 38756</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7429; 22498</t>
+          <t>7124; 22583</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10928; 28399</t>
+          <t>10963; 29466</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16253; 35843</t>
+          <t>17375; 37779</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26455; 44104</t>
+          <t>30290; 50622</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40542</t>
+          <t>44439</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55308</t>
+          <t>60078</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1002; 9818</t>
+          <t>999; 8915</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3126; 14200</t>
+          <t>3120; 14466</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4011; 15464</t>
+          <t>4015; 15365</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6308; 23456</t>
+          <t>9930; 23547</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7237; 21868</t>
+          <t>7092; 21597</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23373; 48178</t>
+          <t>23228; 47105</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12985; 32883</t>
+          <t>13330; 31809</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31489; 51075</t>
+          <t>34992; 55303</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8376; 25484</t>
+          <t>9472; 25847</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28986; 54643</t>
+          <t>29557; 56786</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19703; 42528</t>
+          <t>20683; 43052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36168; 70453</t>
+          <t>47756; 74373</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41570</t>
+          <t>46847</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>55352</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 9750</t>
+          <t>0; 9222</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6951</t>
+          <t>0; 5289</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1837; 10690</t>
+          <t>1694; 11272</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3519; 14179</t>
+          <t>4065; 15443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11567; 28450</t>
+          <t>11289; 28925</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12941; 32873</t>
+          <t>13230; 32553</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10172; 27594</t>
+          <t>9721; 27055</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20515; 63184</t>
+          <t>36204; 61606</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14135; 32631</t>
+          <t>12898; 32372</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14166; 33747</t>
+          <t>13619; 33785</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13582; 33020</t>
+          <t>13873; 33745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31608; 69980</t>
+          <t>42347; 72372</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45806</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53677</t>
+          <t>57693</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1819; 11308</t>
+          <t>1758; 10896</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2098; 12087</t>
+          <t>2863; 13302</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5273</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4164; 15123</t>
+          <t>4511; 15033</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9438; 25488</t>
+          <t>8457; 25077</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16249; 35821</t>
+          <t>16846; 36210</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18768; 41235</t>
+          <t>19307; 41051</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34409; 58316</t>
+          <t>37553; 62358</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12847; 30668</t>
+          <t>13366; 31297</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22030; 43031</t>
+          <t>21893; 45028</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19397; 41613</t>
+          <t>19790; 42399</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42304; 65687</t>
+          <t>46704; 71153</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>153074</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>191837</t>
+          <t>212236</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7344; 22078</t>
+          <t>7324; 22343</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9030; 23462</t>
+          <t>8302; 24472</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12136; 29576</t>
+          <t>12062; 30491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26685; 50183</t>
+          <t>34099; 57097</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43609; 74177</t>
+          <t>43731; 75000</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77799; 118642</t>
+          <t>78955; 117794</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70214; 107871</t>
+          <t>68985; 106283</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>124627; 180486</t>
+          <t>146499; 189643</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54087; 89947</t>
+          <t>54059; 89366</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89615; 132235</t>
+          <t>94271; 137955</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87871; 130168</t>
+          <t>87288; 128433</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>165015; 219937</t>
+          <t>189004; 238462</t>
         </is>
       </c>
     </row>
